--- a/client-report/client-status-report.xlsx
+++ b/client-report/client-status-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="426">
   <si>
     <t>Отчёт по размещению компании в каталогах</t>
   </si>
@@ -57,37 +57,55 @@
     <t>Размещено (подтверждено)</t>
   </si>
   <si>
-    <t>Профиль компании успешно создан и доступен</t>
+    <t>Найден публичный профиль URL / аккаунт подтверждён (Semfirms, FindUsHere, AngelList/Wellfound, Bark.com)</t>
   </si>
   <si>
     <t>Заявка отправлена</t>
   </si>
   <si>
-    <t>Форма размещения заполнена и отправлена, ожидается обработка площадкой</t>
+    <t>Форма отправлена, публикация/профиль ещё не подтверждены (Brownbook, CityLocalPro, DesignRush, GoodFirms, Digital Agency Net, Plantation Chamber)</t>
   </si>
   <si>
     <t>Аккаунт создан</t>
   </si>
   <si>
-    <t>Создан аккаунт, требуется дальнейшее заполнение или публикация профиля</t>
-  </si>
-  <si>
-    <t>Требуется действие</t>
-  </si>
-  <si>
-    <t>Нужен ручной шаг: подтверждение, CAPTCHA, заполнение профиля или другие действия</t>
+    <t>Аккаунт создан, требуется заполнение профиля, публикация контента или завершение регистрации (Crunchbase, Medium, Shopify Partners)</t>
+  </si>
+  <si>
+    <t>Ожидает модерации</t>
+  </si>
+  <si>
+    <t>Площадка получила заявку и выполняет проверку</t>
+  </si>
+  <si>
+    <t>Требуется подтверждение</t>
+  </si>
+  <si>
+    <t>Требуется подтверждение email/телефона для активации размещения</t>
+  </si>
+  <si>
+    <t>Требуется ручное действие</t>
+  </si>
+  <si>
+    <t>Ручной шаг: CAPTCHA, OAuth, зависший submit, партнёрская/плановая заявка или решение пользователя</t>
+  </si>
+  <si>
+    <t>Заблокировано защитой сайта</t>
+  </si>
+  <si>
+    <t>Внешняя блокировка: Cloudflare, CAPTCHA challenge, IP restriction — только ручной заход</t>
   </si>
   <si>
     <t>Не удалось выполнить</t>
   </si>
   <si>
-    <t>Площадка недоступна, заблокирована или возникла техническая проблема</t>
+    <t>Сайт недоступен, регистрация отсутствует (404) или техническая ошибка</t>
   </si>
   <si>
     <t>Не подходит для размещения</t>
   </si>
   <si>
-    <t>Ресурс не является стандартным каталогом компаний или требует другого подхода</t>
+    <t>Ресурс не является стандартным каталогом компаний, требует другого подхода или платного членства</t>
   </si>
   <si>
     <t>Важная информация</t>
@@ -102,9 +120,10 @@
   </si>
   <si>
     <t xml:space="preserve">Приоритет дальнейшей работы:
-1. Завершение площадок, где уже создан аккаунт или отправлена заявка.
-2. Обработка площадок, требующих ручного действия.
-3. Дополнение профилей и получение прямых ссылок на размещения.</t>
+1. Отслеживание SUBMITTED/PENDING: подтвердить email (Brownbook), дождаться модерации (CityLocalPro), проверить публичные профили.
+2. Завершение REGISTERED: заполнить профили Medium, Shopify Partners, 
+3. Обработка NEEDS_MANUAL: TopSEOs (LinkedIn OAuth).
+4. Повторные регистрации для SUBMITTED/REGISTERED/PENDING/BLOCKED НЕ запускать.</t>
   </si>
   <si>
     <t>Каталог</t>
@@ -167,99 +186,108 @@
     <t>Alignable</t>
   </si>
   <si>
+    <t>Требуется действие</t>
+  </si>
+  <si>
+    <t>Ожидает действия</t>
+  </si>
+  <si>
+    <t>Уточнить следующий шаг</t>
+  </si>
+  <si>
+    <t>https://www.alignable.com</t>
+  </si>
+  <si>
+    <t>REGISTERED (аккаунт создан: email itllect.marketing@gmail.com, CAPTCHA вручную). Онбординг остановлен на Business Identity Verification. SMS/Phone Call НЕ используем (не вводить личный телефон). Требуется Manual Verification через Support: Secretary of State registry URL, EIN, NMLS number (не придумывать EIN/NMLS). Публичный профиль НЕ создан. НЕ повторять регистрацию.</t>
+  </si>
+  <si>
+    <t>Superpages</t>
+  </si>
+  <si>
+    <t>Блокировка защитой</t>
+  </si>
+  <si>
+    <t>Manual captcha required (headed-сессия)</t>
+  </si>
+  <si>
+    <t>https://www.superpages.com</t>
+  </si>
+  <si>
+    <t>Закрыто Cloudflare</t>
+  </si>
+  <si>
+    <t>Merchant Circle</t>
+  </si>
+  <si>
+    <t>Ошибка автоматизации</t>
+  </si>
+  <si>
+    <t>Зарегистрировать аккаунт вручную</t>
+  </si>
+  <si>
+    <t>https://www.merchantcircle.com</t>
+  </si>
+  <si>
+    <t>Требуется регистрация мерчанта</t>
+  </si>
+  <si>
+    <t>Local.com</t>
+  </si>
+  <si>
+    <t>Страница не работает</t>
+  </si>
+  <si>
+    <t>https://www.local.com</t>
+  </si>
+  <si>
+    <t>Страница подачи не работает (404)</t>
+  </si>
+  <si>
+    <t>EZlocal</t>
+  </si>
+  <si>
+    <t>https://www.ezlocal.com</t>
+  </si>
+  <si>
+    <t>Brownbook</t>
+  </si>
+  <si>
+    <t>Размещено</t>
+  </si>
+  <si>
+    <t>Профиль создан</t>
+  </si>
+  <si>
+    <t>Проверить публикацию</t>
+  </si>
+  <si>
+    <t>https://www.brownbook.net</t>
+  </si>
+  <si>
+    <t>Размещение подтверждено</t>
+  </si>
+  <si>
+    <t>Opendi</t>
+  </si>
+  <si>
+    <t>No action required (нужен другой IP/VPN)</t>
+  </si>
+  <si>
+    <t>https://www.opendi.us</t>
+  </si>
+  <si>
+    <t>Сайт показывает "Sorry, you have been blocked" — IP/fingerprint блокировка, turnstile не проходит</t>
+  </si>
+  <si>
+    <t>Spoke</t>
+  </si>
+  <si>
     <t>Не подходит</t>
   </si>
   <si>
     <t>Не применимо</t>
   </si>
   <si>
-    <t>https://www.alignable.com</t>
-  </si>
-  <si>
-    <t>Нет открытой формы размещения</t>
-  </si>
-  <si>
-    <t>Superpages</t>
-  </si>
-  <si>
-    <t>Блокировка защитой</t>
-  </si>
-  <si>
-    <t>Manual captcha required (headed-сессия)</t>
-  </si>
-  <si>
-    <t>https://www.superpages.com</t>
-  </si>
-  <si>
-    <t>Закрыто Cloudflare</t>
-  </si>
-  <si>
-    <t>Merchant Circle</t>
-  </si>
-  <si>
-    <t>Ошибка автоматизации</t>
-  </si>
-  <si>
-    <t>Зарегистрировать аккаунт вручную</t>
-  </si>
-  <si>
-    <t>https://www.merchantcircle.com</t>
-  </si>
-  <si>
-    <t>Требуется регистрация мерчанта</t>
-  </si>
-  <si>
-    <t>Local.com</t>
-  </si>
-  <si>
-    <t>Страница не работает</t>
-  </si>
-  <si>
-    <t>https://www.local.com</t>
-  </si>
-  <si>
-    <t>Страница подачи не работает (404)</t>
-  </si>
-  <si>
-    <t>EZlocal</t>
-  </si>
-  <si>
-    <t>https://www.ezlocal.com</t>
-  </si>
-  <si>
-    <t>Brownbook</t>
-  </si>
-  <si>
-    <t>Размещено</t>
-  </si>
-  <si>
-    <t>Профиль создан</t>
-  </si>
-  <si>
-    <t>Проверить публикацию</t>
-  </si>
-  <si>
-    <t>https://www.brownbook.net</t>
-  </si>
-  <si>
-    <t>Размещение подтверждено</t>
-  </si>
-  <si>
-    <t>Opendi</t>
-  </si>
-  <si>
-    <t>No action required (нужен другой IP/VPN)</t>
-  </si>
-  <si>
-    <t>https://www.opendi.us</t>
-  </si>
-  <si>
-    <t>Сайт показывает "Sorry, you have been blocked" — IP/fingerprint блокировка, turnstile не проходит</t>
-  </si>
-  <si>
-    <t>Spoke</t>
-  </si>
-  <si>
     <t>https://spoke.com</t>
   </si>
   <si>
@@ -272,7 +300,16 @@
     <t>https://www.n49.com</t>
   </si>
   <si>
-    <t>Доступ ограничен (403), нет формы размещения</t>
+    <t>Площадка не подходит для размещения</t>
+  </si>
+  <si>
+    <t>FindUsHere</t>
+  </si>
+  <si>
+    <t>https://www.find-us-here.com</t>
+  </si>
+  <si>
+    <t>Профиль создан и публично доступен: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/</t>
   </si>
   <si>
     <t>GoodFirms</t>
@@ -302,9 +339,6 @@
     <t>The Manifest</t>
   </si>
   <si>
-    <t>Ожидает действия</t>
-  </si>
-  <si>
     <t>Зарегистрироваться и подать заявку</t>
   </si>
   <si>
@@ -350,459 +384,447 @@
     <t>Bark.com</t>
   </si>
   <si>
-    <t>Заполнить форму вручную</t>
-  </si>
-  <si>
     <t>https://www.bark.com</t>
   </si>
   <si>
-    <t>Многошаговая форма зависает в автоматизации</t>
+    <t>Аккаунт создан и подтверждён 10.08 (seller/self: spf_id=4708659, user_id=40829222), dashboard live</t>
   </si>
   <si>
     <t>Semfirms</t>
   </si>
   <si>
-    <t>Зарегистрироваться и добавить компанию</t>
-  </si>
-  <si>
     <t>https://semfirms.com</t>
   </si>
   <si>
+    <t>Профиль создан и публично доступен: https://www.semfirms.com/profile/itllect-llc</t>
+  </si>
+  <si>
+    <t>Find Best SEO</t>
+  </si>
+  <si>
+    <t>https://www.findbestseo.com</t>
+  </si>
+  <si>
+    <t>Реестр рейтингов, формы нет</t>
+  </si>
+  <si>
+    <t>TopSEOs</t>
+  </si>
+  <si>
+    <t>Форма заполнена</t>
+  </si>
+  <si>
+    <t>Ожидает завершения</t>
+  </si>
+  <si>
+    <t>Завершить отправку формы</t>
+  </si>
+  <si>
+    <t>https://www.topseos.com</t>
+  </si>
+  <si>
+    <t>Заполнение проходит, submit зависает — нужен ручной клик</t>
+  </si>
+  <si>
+    <t>Influencer Mkt Hub</t>
+  </si>
+  <si>
+    <t>https://influencermarketinghub.com</t>
+  </si>
+  <si>
+    <t>Форма не работает (email-сборщик)</t>
+  </si>
+  <si>
+    <t>Digital Agency Net</t>
+  </si>
+  <si>
+    <t>https://digitalagencynetwork.com</t>
+  </si>
+  <si>
+    <t>Заявка add-agency отправлена</t>
+  </si>
+  <si>
+    <t>FL SBDC Network</t>
+  </si>
+  <si>
+    <t>https://www.floridasbdc.org</t>
+  </si>
+  <si>
+    <t>Консультационный сервис, не каталог</t>
+  </si>
+  <si>
+    <t>Plantation Chamber</t>
+  </si>
+  <si>
+    <t>Ожидать решение по членству</t>
+  </si>
+  <si>
+    <t>https://www.plantationchamber.org</t>
+  </si>
+  <si>
+    <t>Заявка на членство подана</t>
+  </si>
+  <si>
+    <t>Broward County Chamber</t>
+  </si>
+  <si>
+    <t>https://browardchamber.com</t>
+  </si>
+  <si>
+    <t>Страница заявки пустая</t>
+  </si>
+  <si>
+    <t>Ft Lauderdale Chamber</t>
+  </si>
+  <si>
+    <t>https://www.ftlchamber.com</t>
+  </si>
+  <si>
+    <t>Заявка на членство за логином</t>
+  </si>
+  <si>
+    <t>Miami Chamber</t>
+  </si>
+  <si>
+    <t>https://www.miamichamber.com</t>
+  </si>
+  <si>
+    <t>Членство оформляется вручную</t>
+  </si>
+  <si>
+    <t>Nextdoor Business</t>
+  </si>
+  <si>
+    <t>https://business.nextdoor.com</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 2f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: create business page + postcard verify. Not NA.</t>
+  </si>
+  <si>
+    <t>CityLocalPro</t>
+  </si>
+  <si>
+    <t>Завершить submit/captcha</t>
+  </si>
+  <si>
+    <t>https://www.citylocalpro.com</t>
+  </si>
+  <si>
+    <t>Форма заполнена ранее; повторный прогон упал — нужен ручной шаг (reCAPTCHA v2)</t>
+  </si>
+  <si>
+    <t>FL Business Dir</t>
+  </si>
+  <si>
+    <t>https://www.floridabusiness.com</t>
+  </si>
+  <si>
+    <t>South FL Biz Journal</t>
+  </si>
+  <si>
+    <t>Пройти защиту (PR-подача)</t>
+  </si>
+  <si>
+    <t>https://www.bizjournals.com/southflorida</t>
+  </si>
+  <si>
+    <t>City of Plantation</t>
+  </si>
+  <si>
+    <t>https://www.plantation.org/business</t>
+  </si>
+  <si>
+    <t>Муниципальный ресурс</t>
+  </si>
+  <si>
+    <t>Broward County Biz</t>
+  </si>
+  <si>
+    <t>https://www.broward.org/business</t>
+  </si>
+  <si>
+    <t>SCORE Mentor Network</t>
+  </si>
+  <si>
+    <t>https://www.score.org</t>
+  </si>
+  <si>
+    <t>FL DEO Business</t>
+  </si>
+  <si>
+    <t>https://floridajobs.org</t>
+  </si>
+  <si>
+    <t>Гос. портал ресурсов</t>
+  </si>
+  <si>
+    <t>SBA.gov Business</t>
+  </si>
+  <si>
+    <t>https://www.sba.gov</t>
+  </si>
+  <si>
+    <t>Гос. ресурс</t>
+  </si>
+  <si>
+    <t>Semrush Agency Partners</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/agencies</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: agencies.semrush.com has public directory with "List your agency" self-service flow. | DISCOVERY 11.08: /become-a-partner=404; self-service flow: agencies.semrush.com (public dir, no ITllect profile found) → /agencies/get-started/ → signup (email+password+consent, invisible reCAPTCHA) → agency profile. | RESULT 11.08: account created and verified (user ID 30496074, auth works). Agency profile creation requires Agency Partners Platform purchase $90/mo (official KB 1078) - client decision on payment; free-tier has no agency listing path</t>
+  </si>
+  <si>
+    <t>HubSpot Agency Dir</t>
+  </si>
+  <si>
+    <t>https://www.hubspot.com/agencies</t>
+  </si>
+  <si>
+    <t>SUBMITTED 10.08. Flow 2026: /partners/solutions → Get Started → modal hsforms (firstname/lastname/email/phone/website/country_dropdown/employees__c) → POST 200 accepted. Старый URL partners.hubspot.com/agency-partner-application редиректит на ecosystem.hubspot.com/marketplace/solutions; /agency-directory = 404. Листинг в marketplace появляется только после ручного ревью HubSpot (реп-медиатированный онбординг). Эндпоинты: forms.hsforms.com/submissions/v3/public/submit/formsnext/multipart/53/e0bf70bb-7a74-4466-8dc4-8bbe1dfe7037.</t>
+  </si>
+  <si>
+    <t>Shopify Partners</t>
+  </si>
+  <si>
+    <t>Требуется заполнение профиля</t>
+  </si>
+  <si>
+    <t>Заполнить профиль партнёра</t>
+  </si>
+  <si>
+    <t>https://www.shopify.com/partners</t>
+  </si>
+  <si>
+    <t>Partner-аккаунт создан</t>
+  </si>
+  <si>
+    <t>WooCommerce Agency</t>
+  </si>
+  <si>
+    <t>Форма не найдена</t>
+  </si>
+  <si>
+    <t>https://woocommerce.com/agencies</t>
+  </si>
+  <si>
+    <t>Форма не определяется автоматически</t>
+  </si>
+  <si>
+    <t>Webflow Partner</t>
+  </si>
+  <si>
+    <t>https://webflow.com/partners</t>
+  </si>
+  <si>
+    <t>Партнёрская программа (ручное ревью)</t>
+  </si>
+  <si>
+    <t>Mailchimp Partner</t>
+  </si>
+  <si>
+    <t>https://mailchimp.com/partner-directory</t>
+  </si>
+  <si>
+    <t>Партнёрская заявка за логином</t>
+  </si>
+  <si>
+    <t>ActiveCampaign</t>
+  </si>
+  <si>
+    <t>Дозаполнить форму и отправить</t>
+  </si>
+  <si>
+    <t>https://www.activecampaign.com/partners</t>
+  </si>
+  <si>
+    <t>Форма заполнена частично, нет кнопки отправки</t>
+  </si>
+  <si>
+    <t>Stripe Partner</t>
+  </si>
+  <si>
+    <t>Найти путь подачи заявки</t>
+  </si>
+  <si>
+    <t>https://stripe.com/partners</t>
+  </si>
+  <si>
+    <t>Страница заявки без формы</t>
+  </si>
+  <si>
+    <t>Behance</t>
+  </si>
+  <si>
+    <t>https://www.behance.net</t>
+  </si>
+  <si>
+    <t>Dribbble</t>
+  </si>
+  <si>
+    <t>https://dribbble.com</t>
+  </si>
+  <si>
+    <t>Требуется регистрация дизайнера</t>
+  </si>
+  <si>
+    <t>Awwwards</t>
+  </si>
+  <si>
+    <t>Зарегистрироваться (подача платная)</t>
+  </si>
+  <si>
+    <t>https://www.awwwards.com</t>
+  </si>
+  <si>
+    <t>Подача сайта платная</t>
+  </si>
+  <si>
+    <t>CSS Design Awards</t>
+  </si>
+  <si>
+    <t>https://www.cssdesignawards.com</t>
+  </si>
+  <si>
+    <t>SiteInspire</t>
+  </si>
+  <si>
+    <t>https://www.siteinspire.com</t>
+  </si>
+  <si>
+    <t>Редакционная галерея</t>
+  </si>
+  <si>
+    <t>Crunchbase</t>
+  </si>
+  <si>
+    <t>https://www.crunchbase.com</t>
+  </si>
+  <si>
+    <t>Cloudflare 403 — "Sorry, you have been blocked" на /organization/* даже в headed-браузере (11.08); входа нет, креды не сохранены, регистрация OAuth-only — повторные попытки не запускать</t>
+  </si>
+  <si>
+    <t>AngelList/Wellfound</t>
+  </si>
+  <si>
+    <t>https://wellfound.com</t>
+  </si>
+  <si>
+    <t>Профиль компании создан и публично доступен: https://wellfound.com/company/itllect</t>
+  </si>
+  <si>
+    <t>ProductHunt</t>
+  </si>
+  <si>
+    <t>https://www.producthunt.com</t>
+  </si>
+  <si>
+    <t>Запуск через флоу продукта</t>
+  </si>
+  <si>
+    <t>Stack Overflow</t>
+  </si>
+  <si>
+    <t>Пройти защиту / уточнить применимость</t>
+  </si>
+  <si>
+    <t>https://stackoverflow.com/jobs</t>
+  </si>
+  <si>
+    <t>Закрыто Cloudflare; Jobs платные</t>
+  </si>
+  <si>
+    <t>Twitter / X</t>
+  </si>
+  <si>
+    <t>https://twitter.com</t>
+  </si>
+  <si>
+    <t>Требуется верификация по телефону</t>
+  </si>
+  <si>
+    <t>YouTube Channel</t>
+  </si>
+  <si>
+    <t>Канал создан</t>
+  </si>
+  <si>
+    <t>Создать контент канала</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com</t>
+  </si>
+  <si>
+    <t>Brand channel создан</t>
+  </si>
+  <si>
+    <t>Pinterest Business</t>
+  </si>
+  <si>
+    <t>https://business.pinterest.com</t>
+  </si>
+  <si>
+    <t>Требуется бизнес-аккаунт (SPA)</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>https://github.com</t>
+  </si>
+  <si>
+    <t>Платформа для разработки, не каталог</t>
+  </si>
+  <si>
+    <t>Tumblr</t>
+  </si>
+  <si>
+    <t>https://www.tumblr.com</t>
+  </si>
+  <si>
+    <t>Регистрация не прошла автоматически</t>
+  </si>
+  <si>
+    <t>Quora</t>
+  </si>
+  <si>
+    <t>https://www.quora.com</t>
+  </si>
+  <si>
+    <t>Соцсеть, не каталог</t>
+  </si>
+  <si>
+    <t>SlideShare</t>
+  </si>
+  <si>
+    <t>https://www.slideshare.net</t>
+  </si>
+  <si>
+    <t>Регистрация через LinkedIn</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>https://medium.com</t>
+  </si>
+  <si>
+    <t>Cloudflare 403 — "Sorry, you have been blocked" (11.08); сессия не активна, внешняя блокировка — повторные попытки не запускать</t>
+  </si>
+  <si>
+    <t>HubPages</t>
+  </si>
+  <si>
+    <t>Зарегистрироваться и опубликовать материал</t>
+  </si>
+  <si>
+    <t>https://hubpages.com</t>
+  </si>
+  <si>
     <t>Требуется аккаунт</t>
   </si>
   <si>
-    <t>Find Best SEO</t>
-  </si>
-  <si>
-    <t>https://www.findbestseo.com</t>
-  </si>
-  <si>
-    <t>Реестр рейтингов, формы нет</t>
-  </si>
-  <si>
-    <t>TopSEOs</t>
-  </si>
-  <si>
-    <t>Форма заполнена</t>
-  </si>
-  <si>
-    <t>Ожидает завершения</t>
-  </si>
-  <si>
-    <t>Завершить отправку формы</t>
-  </si>
-  <si>
-    <t>https://www.topseos.com</t>
-  </si>
-  <si>
-    <t>Заполнение проходит, submit зависает — нужен ручной клик</t>
-  </si>
-  <si>
-    <t>Influencer Mkt Hub</t>
-  </si>
-  <si>
-    <t>https://influencermarketinghub.com</t>
-  </si>
-  <si>
-    <t>Форма не работает (email-сборщик)</t>
-  </si>
-  <si>
-    <t>Digital Agency Net</t>
-  </si>
-  <si>
-    <t>https://digitalagencynetwork.com</t>
-  </si>
-  <si>
-    <t>Заявка add-agency отправлена</t>
-  </si>
-  <si>
-    <t>FL SBDC Network</t>
-  </si>
-  <si>
-    <t>https://www.floridasbdc.org</t>
-  </si>
-  <si>
-    <t>Консультационный сервис, не каталог</t>
-  </si>
-  <si>
-    <t>Plantation Chamber</t>
-  </si>
-  <si>
-    <t>Ожидать решение по членству</t>
-  </si>
-  <si>
-    <t>https://www.plantationchamber.org</t>
-  </si>
-  <si>
-    <t>Заявка на членство подана</t>
-  </si>
-  <si>
-    <t>Broward County Chamber</t>
-  </si>
-  <si>
-    <t>https://browardchamber.com</t>
-  </si>
-  <si>
-    <t>Страница заявки пустая</t>
-  </si>
-  <si>
-    <t>Ft Lauderdale Chamber</t>
-  </si>
-  <si>
-    <t>https://www.ftlchamber.com</t>
-  </si>
-  <si>
-    <t>Заявка на членство за логином</t>
-  </si>
-  <si>
-    <t>Miami Chamber</t>
-  </si>
-  <si>
-    <t>https://www.miamichamber.com</t>
-  </si>
-  <si>
-    <t>Членство оформляется вручную</t>
-  </si>
-  <si>
-    <t>Nextdoor Business</t>
-  </si>
-  <si>
-    <t>https://business.nextdoor.com</t>
-  </si>
-  <si>
-    <t>Подтверждение по почтовой открытке</t>
-  </si>
-  <si>
-    <t>CityLocalPro</t>
-  </si>
-  <si>
-    <t>Завершить submit/captcha</t>
-  </si>
-  <si>
-    <t>https://www.citylocalpro.com</t>
-  </si>
-  <si>
-    <t>Форма заполнена ранее; повторный прогон упал — нужен ручной шаг (reCAPTCHA v2)</t>
-  </si>
-  <si>
-    <t>FL Business Dir</t>
-  </si>
-  <si>
-    <t>https://www.floridabusiness.com</t>
-  </si>
-  <si>
-    <t>South FL Biz Journal</t>
-  </si>
-  <si>
-    <t>Пройти защиту (PR-подача)</t>
-  </si>
-  <si>
-    <t>https://www.bizjournals.com/southflorida</t>
-  </si>
-  <si>
-    <t>City of Plantation</t>
-  </si>
-  <si>
-    <t>https://www.plantation.org/business</t>
-  </si>
-  <si>
-    <t>Муниципальный ресурс</t>
-  </si>
-  <si>
-    <t>Broward County Biz</t>
-  </si>
-  <si>
-    <t>https://www.broward.org/business</t>
-  </si>
-  <si>
-    <t>SCORE Mentor Network</t>
-  </si>
-  <si>
-    <t>Уточнить следующий шаг</t>
-  </si>
-  <si>
-    <t>https://www.score.org</t>
-  </si>
-  <si>
-    <t>FORM_READY: 29f</t>
-  </si>
-  <si>
-    <t>FL DEO Business</t>
-  </si>
-  <si>
-    <t>https://floridajobs.org</t>
-  </si>
-  <si>
-    <t>Гос. портал ресурсов</t>
-  </si>
-  <si>
-    <t>SBA.gov Business</t>
-  </si>
-  <si>
-    <t>https://www.sba.gov</t>
-  </si>
-  <si>
-    <t>Гос. ресурс</t>
-  </si>
-  <si>
-    <t>Semrush Agency Partners</t>
-  </si>
-  <si>
-    <t>https://www.semrush.com/agencies</t>
-  </si>
-  <si>
-    <t>Партнёрская программа (ручное ревью)</t>
-  </si>
-  <si>
-    <t>HubSpot Agency Dir</t>
-  </si>
-  <si>
-    <t>https://www.hubspot.com/agencies</t>
-  </si>
-  <si>
-    <t>Shopify Partners</t>
-  </si>
-  <si>
-    <t>Требуется заполнение профиля</t>
-  </si>
-  <si>
-    <t>Заполнить профиль партнёра</t>
-  </si>
-  <si>
-    <t>https://www.shopify.com/partners</t>
-  </si>
-  <si>
-    <t>Partner-аккаунт создан</t>
-  </si>
-  <si>
-    <t>WooCommerce Agency</t>
-  </si>
-  <si>
-    <t>Форма не найдена</t>
-  </si>
-  <si>
-    <t>https://woocommerce.com/agencies</t>
-  </si>
-  <si>
-    <t>Форма не определяется автоматически</t>
-  </si>
-  <si>
-    <t>Webflow Partner</t>
-  </si>
-  <si>
-    <t>https://webflow.com/partners</t>
-  </si>
-  <si>
-    <t>Mailchimp Partner</t>
-  </si>
-  <si>
-    <t>https://mailchimp.com/partner-directory</t>
-  </si>
-  <si>
-    <t>Партнёрская заявка за логином</t>
-  </si>
-  <si>
-    <t>ActiveCampaign</t>
-  </si>
-  <si>
-    <t>Дозаполнить форму и отправить</t>
-  </si>
-  <si>
-    <t>https://www.activecampaign.com/partners</t>
-  </si>
-  <si>
-    <t>Форма заполнена частично, нет кнопки отправки</t>
-  </si>
-  <si>
-    <t>Stripe Partner</t>
-  </si>
-  <si>
-    <t>Найти путь подачи заявки</t>
-  </si>
-  <si>
-    <t>https://stripe.com/partners</t>
-  </si>
-  <si>
-    <t>Страница заявки без формы</t>
-  </si>
-  <si>
-    <t>Behance</t>
-  </si>
-  <si>
-    <t>https://www.behance.net</t>
-  </si>
-  <si>
-    <t>Dribbble</t>
-  </si>
-  <si>
-    <t>https://dribbble.com</t>
-  </si>
-  <si>
-    <t>Требуется регистрация дизайнера</t>
-  </si>
-  <si>
-    <t>Awwwards</t>
-  </si>
-  <si>
-    <t>Зарегистрироваться (подача платная)</t>
-  </si>
-  <si>
-    <t>https://www.awwwards.com</t>
-  </si>
-  <si>
-    <t>Подача сайта платная</t>
-  </si>
-  <si>
-    <t>CSS Design Awards</t>
-  </si>
-  <si>
-    <t>https://www.cssdesignawards.com</t>
-  </si>
-  <si>
-    <t>SiteInspire</t>
-  </si>
-  <si>
-    <t>https://www.siteinspire.com</t>
-  </si>
-  <si>
-    <t>Редакционная галерея</t>
-  </si>
-  <si>
-    <t>Crunchbase</t>
-  </si>
-  <si>
-    <t>Заполнить профиль компании</t>
-  </si>
-  <si>
-    <t>https://www.crunchbase.com</t>
-  </si>
-  <si>
-    <t>Регистрация завершена</t>
-  </si>
-  <si>
-    <t>AngelList/Wellfound</t>
-  </si>
-  <si>
-    <t>https://wellfound.com</t>
-  </si>
-  <si>
-    <t>Требуется аккаунт и профиль (SPA)</t>
-  </si>
-  <si>
-    <t>ProductHunt</t>
-  </si>
-  <si>
-    <t>https://www.producthunt.com</t>
-  </si>
-  <si>
-    <t>Запуск через флоу продукта</t>
-  </si>
-  <si>
-    <t>Stack Overflow</t>
-  </si>
-  <si>
-    <t>Пройти защиту / уточнить применимость</t>
-  </si>
-  <si>
-    <t>https://stackoverflow.com/jobs</t>
-  </si>
-  <si>
-    <t>Закрыто Cloudflare; Jobs платные</t>
-  </si>
-  <si>
-    <t>Twitter / X</t>
-  </si>
-  <si>
-    <t>https://twitter.com</t>
-  </si>
-  <si>
-    <t>Требуется верификация по телефону</t>
-  </si>
-  <si>
-    <t>YouTube Channel</t>
-  </si>
-  <si>
-    <t>Канал создан</t>
-  </si>
-  <si>
-    <t>Создать контент канала</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com</t>
-  </si>
-  <si>
-    <t>Brand channel создан</t>
-  </si>
-  <si>
-    <t>Pinterest Business</t>
-  </si>
-  <si>
-    <t>https://business.pinterest.com</t>
-  </si>
-  <si>
-    <t>Требуется бизнес-аккаунт (SPA)</t>
-  </si>
-  <si>
-    <t>GitHub</t>
-  </si>
-  <si>
-    <t>https://github.com</t>
-  </si>
-  <si>
-    <t>Платформа для разработки, не каталог</t>
-  </si>
-  <si>
-    <t>Tumblr</t>
-  </si>
-  <si>
-    <t>https://www.tumblr.com</t>
-  </si>
-  <si>
-    <t>Регистрация не прошла автоматически</t>
-  </si>
-  <si>
-    <t>Quora</t>
-  </si>
-  <si>
-    <t>https://www.quora.com</t>
-  </si>
-  <si>
-    <t>Соцсеть, не каталог</t>
-  </si>
-  <si>
-    <t>SlideShare</t>
-  </si>
-  <si>
-    <t>https://www.slideshare.net</t>
-  </si>
-  <si>
-    <t>Регистрация через LinkedIn</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Требуется публикация</t>
-  </si>
-  <si>
-    <t>Создать страницу компании</t>
-  </si>
-  <si>
-    <t>https://medium.com</t>
-  </si>
-  <si>
-    <t>Аккаунт существует</t>
-  </si>
-  <si>
-    <t>HubPages</t>
-  </si>
-  <si>
-    <t>Зарегистрироваться и опубликовать материал</t>
-  </si>
-  <si>
-    <t>https://hubpages.com</t>
-  </si>
-  <si>
     <t>EzineArticles</t>
   </si>
   <si>
@@ -824,7 +846,7 @@
     <t>https://www.trustpilot.com</t>
   </si>
   <si>
-    <t>Claim через верификацию домена (нужна почта домена)</t>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per NOT_APPLICABLE audit 08.08: claim business + domain verify. Not NA — listing IS possible.</t>
   </si>
   <si>
     <t>Sitejabber</t>
@@ -839,6 +861,15 @@
     <t>Аккаунт создавался ранее; повторный прогон не стартовал (ошибка браузера)</t>
   </si>
   <si>
+    <t>SmartCustomer</t>
+  </si>
+  <si>
+    <t>https://www.smartcustomer.com</t>
+  </si>
+  <si>
+    <t>ЗАВЕРШЕНА на текущем этапе (10.08): итог для клиента — "Регистрация технически выполнена, но площадка требует корпоративный email домена; требуется подтверждение адреса со стороны клиента." Исходный регистрационный email (itllect.marketing@gmail.com) отклонён сервером: mismatch_email (email domain doesn't match website domain). Альтернативный email info@itllect.com использован ВРУЧНУЮ во время диагностики (подмена зафиксирована и разобрана; добавлен generic safeguard: detectEmailDomainMismatch → NEEDS_MANUAL, тест 10/10 PASS). Аккаунт sid 127601 сохранён как CREATED_BUT_WRONG_EMAIL. Статус НЕ VERIFIED_SUCCESS (подтверждение email клиентом не выполнено).</t>
+  </si>
+  <si>
     <t>ProvenExpert</t>
   </si>
   <si>
@@ -884,7 +915,7 @@
     <t>https://www.expressupdate.com</t>
   </si>
   <si>
-    <t>Claim через телефон/почту</t>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: claim InfoGroup listing via phone/postcard. Not NA.</t>
   </si>
   <si>
     <t>Foursquare Business</t>
@@ -893,7 +924,7 @@
     <t>https://business.foursquare.com</t>
   </si>
   <si>
-    <t>Верификация по телефону</t>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: claim venue + phone verify. Business CAN be listed.</t>
   </si>
   <si>
     <t>Показатель</t>
@@ -905,10 +936,10 @@
     <t>Всего каталогов</t>
   </si>
   <si>
-    <t>87 (строк списка клиента; реальных площадок: 75, строк-заголовков секций: 12)</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>87 (строк списка клиента; реальных площадок: 77, строк-заголовков секций: 10)</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>Заявки отправлены</t>
@@ -920,22 +951,22 @@
     <t>Аккаунты созданы</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>21</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>Заблокировано внешними ограничениями</t>
   </si>
   <si>
-    <t>15 (см. лист "External Restrictions")</t>
+    <t>23 (см. лист "External Restrictions")</t>
   </si>
   <si>
     <t>Пояснение (Не подходит)</t>
@@ -947,6 +978,9 @@
     <t>Итого площадок</t>
   </si>
   <si>
+    <t>77</t>
+  </si>
+  <si>
     <t>Directory</t>
   </si>
   <si>
@@ -959,19 +993,16 @@
     <t>Explanation</t>
   </si>
   <si>
+    <t>Search / informational resource</t>
+  </si>
+  <si>
+    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Площадка сменила профиль — не каталог.</t>
+  </si>
+  <si>
     <t>Requires different strategy</t>
   </si>
   <si>
-    <t>Для размещения требуется отдельный подход: создание контента, публикации, партнёрство или ручная заявка. Нет открытой формы размещения.</t>
-  </si>
-  <si>
-    <t>Search / informational resource</t>
-  </si>
-  <si>
-    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Площадка сменила профиль — не каталог.</t>
-  </si>
-  <si>
-    <t>Для размещения требуется отдельный подход: создание контента, публикации, партнёрство или ручная заявка. Доступ ограничен (403), нет формы размещения.</t>
+    <t>Для размещения требуется отдельный подход: создание контента, публикации, партнёрство или ручная заявка.</t>
   </si>
   <si>
     <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Реестр рейтингов, формы нет.</t>
@@ -992,30 +1023,24 @@
     <t>Для размещения требуется отдельный подход: создание контента, публикации, партнёрство или ручная заявка. Членство оформляется вручную.</t>
   </si>
   <si>
+    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Муниципальный ресурс.</t>
+  </si>
+  <si>
+    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Гос. портал ресурсов.</t>
+  </si>
+  <si>
+    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Гос. ресурс.</t>
+  </si>
+  <si>
     <t>Marketplace / Partner platform</t>
   </si>
   <si>
-    <t>Площадка работает через партнёрскую программу или другой механизм, а не через стандартное размещение компании. Подтверждение по почтовой открытке.</t>
-  </si>
-  <si>
-    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Муниципальный ресурс.</t>
-  </si>
-  <si>
-    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Гос. портал ресурсов.</t>
-  </si>
-  <si>
-    <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Гос. ресурс.</t>
-  </si>
-  <si>
     <t>Площадка работает через партнёрскую программу или другой механизм, а не через стандартное размещение компании. Партнёрская программа (ручное ревью).</t>
   </si>
   <si>
     <t>Площадка не является каталогом компаний для добавления бизнес-профиля. Редакционная галерея.</t>
   </si>
   <si>
-    <t>Площадка не является каталогом компаний для добавления бизнес-профиля. Требуется аккаунт и профиль (SPA).</t>
-  </si>
-  <si>
     <t>Для размещения требуется отдельный подход: создание контента, публикации, партнёрство или ручная заявка. Запуск через флоу продукта.</t>
   </si>
   <si>
@@ -1037,54 +1062,75 @@
     <t>Площадка не является каталогом компаний для добавления бизнес-профиля. Форма оказалась email-сборщиком.</t>
   </si>
   <si>
-    <t>Площадка работает через партнёрскую программу или другой механизм, а не через стандартное размещение компании. Claim через верификацию домена (нужна почта домена).</t>
-  </si>
-  <si>
     <t>Ресурс предназначен для поиска информации, а не для создания карточки компании. Агрегатор данных — подача не предусмотрена.</t>
   </si>
   <si>
-    <t>Площадка работает через партнёрскую программу или другой механизм, а не через стандартное размещение компании. Claim через телефон/почту.</t>
-  </si>
-  <si>
-    <t>Площадка работает через партнёрскую программу или другой механизм, а не через стандартное размещение компании. Верификация по телефону.</t>
-  </si>
-  <si>
     <t>Restriction</t>
   </si>
   <si>
     <t>Detail</t>
   </si>
   <si>
+    <t>CAPTCHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEEDS_MANUAL: аккаунт создан (REGISTERED), остановлен на Business Identity Verification — требуется Manual Verification </t>
+  </si>
+  <si>
+    <t>Ручное решение капчи (headed-сессия)</t>
+  </si>
+  <si>
+    <t>SUBMITTED 07.08: заявка отправлена (reCAPTCHA v2 решена вручную, submit прошёл), но публичный профиль НЕ найден: /biz/it</t>
+  </si>
+  <si>
     <t>Cloudflare / IP / access restriction</t>
   </si>
   <si>
+    <t>EXTERNAL BLOCK: Cloudflare hard block on https://www.crunchbase.com/organization/itllect even in headed browser with hum</t>
+  </si>
+  <si>
+    <t>Требуется другой IP/VPN или ручной заход</t>
+  </si>
+  <si>
+    <t>Подтверждено в headed-сессии 31.07 (turnstile решён, submit отправлен)</t>
+  </si>
+  <si>
+    <t>Cloudflare block</t>
+  </si>
+  <si>
+    <t>EXTERNAL BLOCK: Cloudflare hard block 'Sorry, you have been blocked' even in headed browser with human-medium profile. E</t>
+  </si>
+  <si>
+    <t>CF turnstile verification failed after multiple attempts in headed browser</t>
+  </si>
+  <si>
+    <t>Account created (user ID 30496074, itllect.marketing@gmail.com, logged in). Agency listing requires paid Agency Partners</t>
+  </si>
+  <si>
     <t>EXTERNAL BLOCK — Cloudflare/access restriction; possible IP reputation block; automation detected. Домен недоступен, пов</t>
   </si>
   <si>
-    <t>Требуется другой IP/VPN или ручной заход</t>
+    <t>Cloudflare not passable in headed browser either (human action timeout)</t>
+  </si>
+  <si>
+    <t>Site unavailable</t>
+  </si>
+  <si>
+    <t>Site unreachable (chrome-error)</t>
+  </si>
+  <si>
+    <t>No action required (сайт недоступен)</t>
   </si>
   <si>
     <t>page.waitForTimeout: Target page, context or browser has been closed</t>
   </si>
   <si>
-    <t>Site unavailable</t>
-  </si>
-  <si>
-    <t>Site unreachable (chrome-error)</t>
-  </si>
-  <si>
-    <t>No action required (сайт недоступен)</t>
-  </si>
-  <si>
-    <t>CAPTCHA</t>
-  </si>
-  <si>
-    <t>Ручное решение капчи (headed-сессия)</t>
-  </si>
-  <si>
     <t>Human action timeout (180s)</t>
   </si>
   <si>
+    <t>Block on Clutch.co (Cloudflare challenge loop /get-listed)</t>
+  </si>
+  <si>
     <t>CF blocked in headless; needs headed stealth + manual solve</t>
   </si>
   <si>
@@ -1100,112 +1146,160 @@
     <t>Причина</t>
   </si>
   <si>
+    <t>BLOCKED</t>
+  </si>
+  <si>
+    <t>BLOCKED: Cloudflare 403 — 'Sorry, you have been blocked'; требуется ручной заход</t>
+  </si>
+  <si>
+    <t>Cloudflare</t>
+  </si>
+  <si>
+    <t>BLOCKED: Cloudflare 403 — 'Performing security verification'; требуется ручной заход</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NEEDS_MANUAL</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>Заявка подана в headed-сессии 31.07 (CF пройден); повторный заход заблокирован (Cloudflare/IP) — статус не подтверждён</t>
-  </si>
-  <si>
-    <t>Cloudflare</t>
+    <t>403/404</t>
+  </si>
+  <si>
+    <t>требуется регистрация/вход</t>
+  </si>
+  <si>
+    <t>claim-listing → 404 (Page not found), форма нерабочая</t>
   </si>
   <si>
     <t>SUBMITTED</t>
   </si>
   <si>
+    <t>SUBMITTED 07.08: заявка отправлена, профиль НЕ опубликован (поиск: Results Found 0) — ожидает email-подтверждения на info@itllect-agency.com / модерации</t>
+  </si>
+  <si>
+    <t>REPROBE 08.08: CF turnstile — multiple headed attempts failed, verification not passable; stay BLOCKED</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE</t>
+  </si>
+  <si>
+    <t>REPROBE 08.08: accessible but no add business form — not a business directory; status NOT_APPLICABLE</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: профиль создан и публично доступен (18+ млн бизнесов в каталоге)</t>
+  </si>
+  <si>
+    <t>Регистрация пройдена, профиль агентства заполнен вручную, отправлен</t>
+  </si>
+  <si>
+    <t>CF blocked in headless; needs headed stealth + manual solve; REPROBE 2026-08-08: Site accessible, form detected — needs submission attempt; SUBMIT FAILED 08.08: CF not passable in headed mode</t>
+  </si>
+  <si>
+    <t>The Manifest has no own form (/listings/list-your-company = 404). /get-listed explains: registration via Clutch.co. CTA 'Create a Free Profile' -&gt; https://vendor.clutch.co/profile/create/basic (Basic tier, free). Main clutch.co/get-listed loads (CF clears ~30s; tiers: Basic Free / Verified $499/yr / Advertiser). But vendor.clutch.co CF challenge-loop: 'Verification successful. Waiting for vendor.clutch.co to respond' — origin does not respond (Ray ID a27c85757b9b543b). 2 attempts waited 120s and 288s, both stuck. 3 false-positive SUBMITTED outcomes reverted (0 fields). BLOCKED per site-handling rules — no loop reopening. Manual human session in regular browser may work.</t>
+  </si>
+  <si>
+    <t>сайт недоступен</t>
+  </si>
+  <si>
     <t>SUCCESS</t>
   </si>
   <si>
-    <t>Форма claim/add business заполнена, заявка подана (человек подтвердил)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Add business подан (CF решён человеком), подтверждено</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE</t>
-  </si>
-  <si>
-    <t>Площадка не подходит для размещения</t>
-  </si>
-  <si>
-    <t>page.screenshot: Timeout 30000ms exceeded.</t>
-  </si>
-  <si>
-    <t>требуется регистрация/вход</t>
-  </si>
-  <si>
-    <t>claim-listing → 404 (Page not found), форма нерабочая</t>
-  </si>
-  <si>
-    <t>VERIFIED_SUCCESS</t>
-  </si>
-  <si>
-    <t>Профиль создан автоматически (44 поля, 0 ошибок) — размещение подтверждено</t>
-  </si>
-  <si>
-    <t>EXTERNAL BLOCK — Cloudflare/access restriction; IP/fingerprint блокировка, turnstile не проходит ("Sorry, you have been blocked")</t>
-  </si>
-  <si>
-    <t>Регистрация пройдена, профиль агентства заполнен вручную, отправлен</t>
-  </si>
-  <si>
-    <t>NEEDS_MANUAL</t>
-  </si>
-  <si>
-    <t>Окно ручного действия истекло (180с) — требуется повтор</t>
-  </si>
-  <si>
-    <t>сайт недоступен</t>
-  </si>
-  <si>
-    <t>SPA-форма 35f открывается; заполнение медленное, зависает — нужен ручной шаг</t>
+    <t>VERIFIED_SUCCESS: аккаунт продавца создан 2026-08-10 13:39:13 (seller spf_id=4708659, user_id=40829222) — подтверждено через api.bark.com/seller/self. Dashboard live (15 leads, 3 services, 1 location). Регистрация серверная на шаге address-Next; профиль ITllect / Plantation FL 33324. Повторная регистрация НЕ нужна.</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: профиль создан и публично доступен</t>
+  </si>
+  <si>
+    <t>Форма жива на /registration (Drupal); заполнение проходит, submit зависает — нужен ручной шаг</t>
+  </si>
+  <si>
+    <t>Регистрация пройдена, заявка add-agency отправлена</t>
+  </si>
+  <si>
+    <t>Заявка на членство подана (человек подтвердил)</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: create business page + postcard PIN verification. Local directory listing possible.</t>
+  </si>
+  <si>
+    <t>SUBMITTED 07.08: заявка отправлена (reCAPTCHA v2 решена вручную), профиль НЕ опубликован (поиск: No result) — ожидает модерации</t>
+  </si>
+  <si>
+    <t>CAPTCHA (recaptcha_v2)</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: list agency on agencies.semrush.com self-service flow.</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: partner application leads to public agency directory listing.</t>
+  </si>
+  <si>
+    <t>REGISTERED</t>
+  </si>
+  <si>
+    <t>Form fields not found by Playwright</t>
   </si>
   <si>
     <t>Login/registration required</t>
   </si>
   <si>
-    <t>Форма жива на /registration (Drupal); заполнение проходит, submit зависает — нужен ручной шаг</t>
-  </si>
-  <si>
-    <t>Регистрация пройдена, заявка add-agency отправлена</t>
-  </si>
-  <si>
-    <t>Заявка на членство подана (человек подтвердил)</t>
-  </si>
-  <si>
-    <t>Форма 17f заполнена ранее; повторный прогон упал (краш браузера) — нужен ручной шаг (reCAPTCHA v2)</t>
-  </si>
-  <si>
-    <t>CAPTCHA (recaptcha_v2)</t>
-  </si>
-  <si>
-    <t>PENDING</t>
-  </si>
-  <si>
-    <t>REGISTERED</t>
-  </si>
-  <si>
-    <t>Form fields not found by Playwright</t>
-  </si>
-  <si>
-    <t>Сайт ожил после DEAD; partner-форма 21f заполнена частично, submit-кнопки нет</t>
-  </si>
-  <si>
-    <t>Аккаунт создан в headed-сессии; CF обойдён вручную</t>
-  </si>
-  <si>
-    <t>Brand channel создан (человек подтвердил)</t>
-  </si>
-  <si>
-    <t>Аккаунт создан, email подтверждён, draft о компании готов</t>
+    <t>Partner ecosystem (reseller/commission program), не бизнес-каталог — /partner содержит только sales-lead формы (Demo/Pricing/Trial), публичного каталога агентств нет</t>
+  </si>
+  <si>
+    <t>Требуется найти способ подачи партнёрской заявки.</t>
+  </si>
+  <si>
+    <t>NOT_RELEVANT</t>
+  </si>
+  <si>
+    <t>Площадка ориентирована на дизайнерские профили и портфолио; подходящего профиля компании/SEO-агентства для размещения ITllect в рамках данного заказа не найдено.</t>
+  </si>
+  <si>
+    <t>BLOCKED 11.08: Cloudflare 403 — 'Sorry, you have been blocked' на /organization/itllect даже в headed-браузере с профилем human-crunchbase (evidence: human-submit-out/crunchbase/cb-org-headed.png). Главная грузится, но все глубокие пути (/organization/*, /search/*) блокируются. Сессионной cookie нет, логины не сохранены, пароль не найден; по документации регистрация OAuth-only; почта регистрации недоступна (IMAP invalid). Повторные попытки НЕ запускать, новый аккаунт НЕ создавать.</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: company profile создан и публично доступен — https://wellfound.com/company/itllect (slug itllect, location Coral Springs, Software, 1-10, Founder: Dmitrii Dovzhenko). Регистрация аккаунта itllect.marketing@gmail.com + профиль заполнены в headed-сессии 11.08; step 1 onboarding завершён, invite-шаг пропущен.</t>
+  </si>
+  <si>
+    <t>YouTube является видеоплатформой, а не бизнес-каталогом; создание брендового канала не соответствует цели текущего заказа по добавлению компании в каталоги.</t>
+  </si>
+  <si>
+    <t>Контентная/социальная платформа, а не релевантный бизнес-каталог для текущей задачи размещения компании.</t>
+  </si>
+  <si>
+    <t>BLOCKED 11.08: Cloudflare 403 — 'Sorry, you have been blocked' (headed). Сессия не активна, повторные заходы блокируются. Повторные попытки НЕ запускать, новый аккаунт НЕ создавать.</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: claim business + domain verification required. Listing IS possible.</t>
   </si>
   <si>
     <t>CAPTCHA (turnstile)</t>
   </si>
   <si>
+    <t>Регистрация технически выполнена, но площадка требует корпоративный email домена; требуется подтверждение адреса со стороны клиента.</t>
+  </si>
+  <si>
+    <t>REPROBE 08.08: site accessible (en-us/), form 10 fields detected, EMAIL fields absent — HUMAN ACTION timeout; stay NEEDS_MANUAL</t>
+  </si>
+  <si>
     <t>Сайт ожил после DEAD; claim-listing закрыт Cloudflare; повторный прогон упал (краш браузера)</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: claim InfoGroup citation listing via phone/postcard.</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: claim venue + phone verification required. Business CAN be listed.</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1681,7 +1775,7 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
@@ -1692,7 +1786,7 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
@@ -1703,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>17</v>
@@ -1714,7 +1808,7 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -1725,7 +1819,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -1736,48 +1830,64 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="16" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
     </row>
@@ -1786,22 +1896,39 @@
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
+    <row r="27" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A18:C21"/>
-    <mergeCell ref="A24:C27"/>
+    <mergeCell ref="A22:C25"/>
+    <mergeCell ref="A28:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1810,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1823,1522 +1950,1562 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F23" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F27" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F29" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F32" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F34" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F35" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F36" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F37" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F38" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F39" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F41" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E42" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F42" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F43" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="E44" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F44" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F45" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F46" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F47" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E48" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="E49" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F50" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D51" t="s">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="E51" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="E52" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E53" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F53" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F54" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F55" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E56" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F56" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D57" t="s">
-        <v>226</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F57" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>36</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F58" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>233</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
-        <v>234</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F59" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>242</v>
       </c>
       <c r="E60" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B61" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F61" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F62" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E63" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F63" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F64" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B65" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>253</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
-        <v>254</v>
+        <v>42</v>
       </c>
       <c r="E65" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F65" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>258</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
+        <v>264</v>
       </c>
       <c r="E67" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F67" t="s">
-        <v>98</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F68" t="s">
-        <v>264</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E69" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F69" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C70" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>269</v>
+        <v>56</v>
       </c>
       <c r="E70" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F70" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D71" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E71" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D72" t="s">
-        <v>277</v>
+        <v>56</v>
       </c>
       <c r="E72" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F72" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>283</v>
       </c>
       <c r="E73" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F73" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C74" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
+        <v>287</v>
       </c>
       <c r="E74" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F74" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C75" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E75" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F75" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E76" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F76" t="s">
-        <v>290</v>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>295</v>
+      </c>
+      <c r="B77" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D77" t="s">
+        <v>56</v>
+      </c>
+      <c r="E77" t="s">
+        <v>296</v>
+      </c>
+      <c r="F77" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>298</v>
+      </c>
+      <c r="B78" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" t="s">
+        <v>56</v>
+      </c>
+      <c r="E78" t="s">
+        <v>299</v>
+      </c>
+      <c r="F78" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3358,98 +3525,98 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3460,7 +3627,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3471,436 +3638,338 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
         <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C12" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="D14" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D15" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D16" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D17" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="C18" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D18" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="B19" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D19" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D20" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="C21" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D21" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="B22" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D22" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D23" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D24" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>249</v>
-      </c>
-      <c r="B25" t="s">
-        <v>250</v>
-      </c>
-      <c r="C25" t="s">
-        <v>318</v>
-      </c>
-      <c r="D25" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C26" t="s">
-        <v>318</v>
-      </c>
-      <c r="D26" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>265</v>
-      </c>
-      <c r="B27" t="s">
-        <v>266</v>
-      </c>
-      <c r="C27" t="s">
-        <v>323</v>
-      </c>
-      <c r="D27" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>280</v>
-      </c>
-      <c r="B28" t="s">
-        <v>281</v>
-      </c>
-      <c r="C28" t="s">
-        <v>314</v>
-      </c>
-      <c r="D28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B29" t="s">
-        <v>284</v>
-      </c>
-      <c r="C29" t="s">
-        <v>314</v>
-      </c>
-      <c r="D29" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>285</v>
-      </c>
-      <c r="B30" t="s">
-        <v>286</v>
-      </c>
-      <c r="C30" t="s">
-        <v>323</v>
-      </c>
-      <c r="D30" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>288</v>
-      </c>
-      <c r="B31" t="s">
-        <v>289</v>
-      </c>
-      <c r="C31" t="s">
-        <v>323</v>
-      </c>
-      <c r="D31" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -3911,7 +3980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3923,274 +3992,410 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D4" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E4" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D5" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="E6" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="E8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>270</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" t="s">
         <v>351</v>
-      </c>
-      <c r="D9" t="s">
-        <v>347</v>
-      </c>
-      <c r="E9" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D10" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D11" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E11" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="D12" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D13" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="E13" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>260</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
-        <v>261</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="D14" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="E14" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D15" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E15" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E16" t="s">
-        <v>346</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" t="s">
+        <v>367</v>
+      </c>
+      <c r="E17" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>353</v>
+      </c>
+      <c r="D18" t="s">
+        <v>366</v>
+      </c>
+      <c r="E18" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>353</v>
+      </c>
+      <c r="D19" t="s">
+        <v>368</v>
+      </c>
+      <c r="E19" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" t="s">
+        <v>363</v>
+      </c>
+      <c r="D20" t="s">
+        <v>364</v>
+      </c>
+      <c r="E20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" t="s">
+        <v>363</v>
+      </c>
+      <c r="D21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E21" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22" t="s">
+        <v>364</v>
+      </c>
+      <c r="E22" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>165</v>
+      </c>
+      <c r="B23" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" t="s">
+        <v>353</v>
+      </c>
+      <c r="D23" t="s">
+        <v>369</v>
+      </c>
+      <c r="E23" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" t="s">
+        <v>353</v>
+      </c>
+      <c r="D24" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4201,7 +4406,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -4214,359 +4419,359 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E2" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="F2" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E3" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="F3" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D4" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F4" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D5" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E5" t="s">
-        <v>368</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D6" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E6" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="F6" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="F7" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E8" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F8" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D9" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E9" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="F9" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="E10" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F10" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D11" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E11" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F11" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D12" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E12" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D13" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E13" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="F13" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="D14" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>390</v>
       </c>
       <c r="F14" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="D15" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="E15" t="s">
-        <v>375</v>
+        <v>98</v>
       </c>
       <c r="F15" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="E16" t="s">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="F16" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
+        <v>374</v>
+      </c>
+      <c r="D17" t="s">
+        <v>374</v>
+      </c>
+      <c r="E17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F17" t="s">
         <v>376</v>
-      </c>
-      <c r="D17" t="s">
-        <v>376</v>
-      </c>
-      <c r="E17" t="s">
-        <v>377</v>
-      </c>
-      <c r="F17" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D18" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>393</v>
       </c>
       <c r="F18" t="s">
         <v>378</v>
@@ -4574,619 +4779,619 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D19" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E19" t="s">
-        <v>347</v>
+        <v>109</v>
       </c>
       <c r="F19" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D20" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E20" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="F20" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D21" t="s">
+        <v>374</v>
+      </c>
+      <c r="E21" t="s">
+        <v>369</v>
+      </c>
+      <c r="F21" t="s">
         <v>376</v>
-      </c>
-      <c r="D21" t="s">
-        <v>376</v>
-      </c>
-      <c r="E21" t="s">
-        <v>379</v>
-      </c>
-      <c r="F21" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="D22" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="E22" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="F22" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="D23" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="E23" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="F23" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D24" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E24" t="s">
-        <v>381</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D25" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E25" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="F25" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="D26" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E26" t="s">
-        <v>382</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="D27" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="E27" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="F27" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="D28" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E28" t="s">
-        <v>383</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="D29" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="E29" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="F29" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D30" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E30" t="s">
-        <v>377</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D31" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E31" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D32" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E32" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="D33" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="E33" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="F33" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C34" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="D34" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="E34" t="s">
-        <v>98</v>
+        <v>402</v>
       </c>
       <c r="F34" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D35" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E35" t="s">
-        <v>354</v>
+        <v>109</v>
       </c>
       <c r="F35" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D36" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E36" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F36" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D37" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E37" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F37" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D38" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E38" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D39" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E39" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D40" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E40" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C41" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D41" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E41" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F41" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C42" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D42" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E42" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="F42" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C43" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D43" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="E43" t="s">
-        <v>183</v>
+        <v>405</v>
       </c>
       <c r="F43" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B44" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C44" t="s">
-        <v>359</v>
+        <v>406</v>
       </c>
       <c r="D44" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E44" t="s">
-        <v>388</v>
+        <v>191</v>
       </c>
       <c r="F44" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C45" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D45" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="E45" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="F45" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C46" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D46" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E46" t="s">
-        <v>380</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C47" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D47" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E47" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="F47" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C48" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D48" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E48" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="F48" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B49" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C49" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D49" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>410</v>
       </c>
       <c r="F49" t="s">
         <v>378</v>
@@ -5194,542 +5399,582 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C50" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D50" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E50" t="s">
-        <v>347</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C51" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D51" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="E51" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="F51" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C52" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D52" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E52" t="s">
-        <v>98</v>
+        <v>408</v>
       </c>
       <c r="F52" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C53" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="E53" t="s">
-        <v>368</v>
+        <v>109</v>
       </c>
       <c r="F53" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B54" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C54" t="s">
         <v>387</v>
       </c>
       <c r="D54" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E54" t="s">
-        <v>390</v>
+        <v>92</v>
       </c>
       <c r="F54" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B55" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C55" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D55" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E55" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="F55" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C56" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="E56" t="s">
-        <v>368</v>
+        <v>414</v>
       </c>
       <c r="F56" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B57" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C57" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D57" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E57" t="s">
-        <v>354</v>
+        <v>92</v>
       </c>
       <c r="F57" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D58" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E58" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F58" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C59" t="s">
         <v>387</v>
       </c>
       <c r="D59" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E59" t="s">
-        <v>391</v>
+        <v>92</v>
       </c>
       <c r="F59" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C60" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D60" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="E60" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="F60" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B61" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C61" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D61" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E61" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F61" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C62" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="D62" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="E62" t="s">
-        <v>347</v>
+        <v>92</v>
       </c>
       <c r="F62" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B63" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C63" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="D63" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="E63" t="s">
-        <v>368</v>
+        <v>416</v>
       </c>
       <c r="F63" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B64" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C64" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D64" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E64" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F64" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B65" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
         <v>387</v>
       </c>
       <c r="D65" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E65" t="s">
-        <v>392</v>
+        <v>92</v>
       </c>
       <c r="F65" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C66" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D66" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E66" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="F66" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C67" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D67" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>418</v>
       </c>
       <c r="F67" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B68" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C68" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D68" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="E68" t="s">
-        <v>368</v>
+        <v>109</v>
       </c>
       <c r="F68" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C69" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D69" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E69" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F69" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C70" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D70" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E70" t="s">
-        <v>271</v>
+        <v>419</v>
       </c>
       <c r="F70" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B71" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C71" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="D71" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="E71" t="s">
-        <v>377</v>
+        <v>278</v>
       </c>
       <c r="F71" t="s">
-        <v>370</v>
+        <v>420</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B72" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C72" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D72" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E72" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="F72" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B73" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C73" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D73" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="E73" t="s">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="F73" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C74" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D74" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E74" t="s">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="F74" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B75" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C75" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D75" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E75" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F75" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B76" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C76" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="D76" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E76" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="F76" t="s">
-        <v>365</v>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>295</v>
+      </c>
+      <c r="B77" t="s">
+        <v>296</v>
+      </c>
+      <c r="C77" t="s">
+        <v>379</v>
+      </c>
+      <c r="D77" t="s">
+        <v>379</v>
+      </c>
+      <c r="E77" t="s">
+        <v>424</v>
+      </c>
+      <c r="F77" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>298</v>
+      </c>
+      <c r="B78" t="s">
+        <v>299</v>
+      </c>
+      <c r="C78" t="s">
+        <v>379</v>
+      </c>
+      <c r="D78" t="s">
+        <v>379</v>
+      </c>
+      <c r="E78" t="s">
+        <v>425</v>
+      </c>
+      <c r="F78" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/client-report/client-status-report.xlsx
+++ b/client-report/client-status-report.xlsx
@@ -1266,7 +1266,7 @@
     <t>BLOCKED 11.08: Cloudflare 403 — 'Sorry, you have been blocked' на /organization/itllect даже в headed-браузере с профилем human-crunchbase (evidence: human-submit-out/crunchbase/cb-org-headed.png). Главная грузится, но все глубокие пути (/organization/*, /search/*) блокируются. Сессионной cookie нет, логины не сохранены, пароль не найден; по документации регистрация OAuth-only; почта регистрации недоступна (IMAP invalid). Повторные попытки НЕ запускать, новый аккаунт НЕ создавать.</t>
   </si>
   <si>
-    <t>VERIFIED_SUCCESS: company profile создан и публично доступен — https://wellfound.com/company/itllect (slug itllect, location Coral Springs, Software, 1-10, Founder: Dmitrii Dovzhenko). Регистрация аккаунта itllect.marketing@gmail.com + профиль заполнены в headed-сессии 11.08; step 1 onboarding завершён, invite-шаг пропущен.</t>
+    <t>VERIFIED_SUCCESS: company profile создан и публично доступен — https://wellfound.com/company/itllect (slug itllect, location Coral Springs, Software, 1-10, Founder: [REDACTED]). Регистрация аккаунта itllect.marketing@gmail.com + профиль заполнены в headed-сессии 11.08; step 1 onboarding завершён, invite-шаг пропущен.</t>
   </si>
   <si>
     <t>YouTube является видеоплатформой, а не бизнес-каталогом; создание брендового канала не соответствует цели текущего заказа по добавлению компании в каталоги.</t>
@@ -1931,7 +1931,7 @@
     <mergeCell ref="A28:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3510,7 +3510,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3621,7 +3621,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3974,7 +3974,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4400,7 +4400,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5979,6 +5979,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>